--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/NEW_MEXICO_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/NEW_MEXICO_2020.xlsx
@@ -1446,7 +1446,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Guerero</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C61">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Praxedis G. Guerero</t>
+          <t>Praxedis G. Guerrero</t>
         </is>
       </c>
       <c r="C84">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C132">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C158">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C189">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C194">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Tixtla De Guerero</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C239">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C294">
